--- a/Group0_1LibraryDW/09_Source_Data/digital_usage.xlsx
+++ b/Group0_1LibraryDW/09_Source_Data/digital_usage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITLDM801\Group03_LibraryDW\09_Source_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITLDM801\Group0_1LibraryDW\09_Source_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5586F66E-8DE0-4A59-924C-E5A249CA07B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9B7F01-18F7-4188-9D49-63EB9A75A053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{EF303B4F-7126-46E8-AB64-20AC5B7A5540}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>04/10/2024</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Laws</t>
   </si>
 </sst>
 </file>
@@ -691,7 +697,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
@@ -709,7 +715,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1">
         <v>8</v>
